--- a/25-새서울철도-강남구-보고서.xlsx
+++ b/25-새서울철도-강남구-보고서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275013E1-92B9-4172-B8B7-42DC84131B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A51E54-BF2A-49F6-AFC8-420B7941421B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23040" yWindow="12" windowWidth="23256" windowHeight="12972" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="121">
   <si>
     <t>시행년도</t>
   </si>
@@ -2341,6 +2341,114 @@
     <t>지번 주소
 (도로명 주소)</t>
     <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>신사동 501</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 17</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 17-4</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 논현동 18-3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 19-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 49</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 49-17</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 50</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 50-1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 120</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 164</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 164-4</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 165</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 165-8</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 199</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>논현동 200-7</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 808</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 808-4</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 809-12</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 814-5</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 814-6</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 815</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 815-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 815-5</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 820</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 820-8</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>역삼동 820-9</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2570,16 +2678,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2916,15 +3024,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
+      <xdr:colOff>161381</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>39460</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2868386</xdr:colOff>
+      <xdr:colOff>2866481</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>1628775</xdr:rowOff>
+      <xdr:rowOff>1630680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2954,8 +3062,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13579929" y="8870496"/>
-          <a:ext cx="2705100" cy="1589315"/>
+          <a:off x="13670552" y="8867774"/>
+          <a:ext cx="2705100" cy="1591220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2979,13 +3087,13 @@
       <xdr:col>17</xdr:col>
       <xdr:colOff>149679</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>25854</xdr:rowOff>
+      <xdr:rowOff>27759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>2854779</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>1615168</xdr:rowOff>
+      <xdr:rowOff>1618978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3015,8 +3123,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13566322" y="10503354"/>
-          <a:ext cx="2705100" cy="1589314"/>
+          <a:off x="13658850" y="10499816"/>
+          <a:ext cx="2705100" cy="1591219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3831,15 +3939,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
+      <xdr:colOff>178798</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>39461</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2881993</xdr:colOff>
+      <xdr:colOff>2883898</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>1628775</xdr:rowOff>
+      <xdr:rowOff>1630680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3869,8 +3977,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593536" y="33567461"/>
-          <a:ext cx="2705100" cy="1589314"/>
+          <a:off x="13687969" y="33523918"/>
+          <a:ext cx="2705100" cy="1591219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3953,15 +4061,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
+      <xdr:colOff>161381</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>25853</xdr:rowOff>
+      <xdr:rowOff>27758</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2868386</xdr:colOff>
+      <xdr:colOff>2866481</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>1615168</xdr:rowOff>
+      <xdr:rowOff>1618978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3991,8 +4099,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13579929" y="36846782"/>
-          <a:ext cx="2705100" cy="1589315"/>
+          <a:off x="13670552" y="36799701"/>
+          <a:ext cx="2705100" cy="1591220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4014,15 +4122,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
+      <xdr:colOff>161381</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>25854</xdr:rowOff>
+      <xdr:rowOff>27759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2868386</xdr:colOff>
+      <xdr:colOff>2866481</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>1615168</xdr:rowOff>
+      <xdr:rowOff>1618978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4052,8 +4160,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13579929" y="38493247"/>
-          <a:ext cx="2705100" cy="1589314"/>
+          <a:off x="13670552" y="38443445"/>
+          <a:ext cx="2705100" cy="1591219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4136,15 +4244,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
+      <xdr:colOff>161381</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>25854</xdr:rowOff>
+      <xdr:rowOff>27759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2868386</xdr:colOff>
+      <xdr:colOff>2866481</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>1615168</xdr:rowOff>
+      <xdr:rowOff>1618978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4174,8 +4282,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13579929" y="41786175"/>
-          <a:ext cx="2705100" cy="1589314"/>
+          <a:off x="13670552" y="41730930"/>
+          <a:ext cx="2705100" cy="1591219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4197,15 +4305,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176892</xdr:colOff>
+      <xdr:colOff>178797</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>25853</xdr:rowOff>
+      <xdr:rowOff>27758</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2881992</xdr:colOff>
+      <xdr:colOff>2883897</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>1615168</xdr:rowOff>
+      <xdr:rowOff>1618978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4235,8 +4343,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593535" y="43432639"/>
-          <a:ext cx="2705100" cy="1589315"/>
+          <a:off x="13687968" y="43374672"/>
+          <a:ext cx="2705100" cy="1591220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4258,15 +4366,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>176892</xdr:colOff>
+      <xdr:colOff>178797</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>25854</xdr:rowOff>
+      <xdr:rowOff>27759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>2881992</xdr:colOff>
+      <xdr:colOff>2883897</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>1615168</xdr:rowOff>
+      <xdr:rowOff>1618978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4296,8 +4404,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13593535" y="45079104"/>
-          <a:ext cx="2705100" cy="1589314"/>
+          <a:off x="13687968" y="45018416"/>
+          <a:ext cx="2705100" cy="1591219"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6297,7 +6405,9 @@
         <v>일반</v>
       </c>
       <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
+      <c r="Q6" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="R6" s="25"/>
       <c r="S6" s="7" t="s">
         <v>27</v>
@@ -6361,7 +6471,9 @@
       <c r="P7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="R7" s="25"/>
       <c r="S7" s="7" t="s">
         <v>29</v>
@@ -6423,7 +6535,9 @@
         <v>일반</v>
       </c>
       <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
+      <c r="Q8" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="R8" s="25"/>
       <c r="S8" s="7" t="s">
         <v>31</v>
@@ -6485,7 +6599,9 @@
         <v>일반</v>
       </c>
       <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
+      <c r="Q9" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="R9" s="25"/>
       <c r="S9" s="9" t="s">
         <v>32</v>
@@ -6547,7 +6663,9 @@
         <v>일반</v>
       </c>
       <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
+      <c r="Q10" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="R10" s="25"/>
       <c r="S10" s="7" t="s">
         <v>33</v>
@@ -6609,7 +6727,9 @@
         <v>일반</v>
       </c>
       <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="R11" s="25"/>
       <c r="S11" s="9" t="s">
         <v>34</v>
@@ -6671,7 +6791,9 @@
         <v>일반</v>
       </c>
       <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
+      <c r="Q12" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="R12" s="25"/>
       <c r="S12" s="7" t="s">
         <v>35</v>
@@ -6733,7 +6855,9 @@
         <v>일반</v>
       </c>
       <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
+      <c r="Q13" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="R13" s="25"/>
       <c r="S13" s="7" t="s">
         <v>36</v>
@@ -6797,7 +6921,9 @@
       <c r="P14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q14" s="6"/>
+      <c r="Q14" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="R14" s="25"/>
       <c r="S14" s="7" t="s">
         <v>36</v>
@@ -6859,7 +6985,9 @@
         <v>일반</v>
       </c>
       <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
+      <c r="Q15" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="R15" s="25"/>
       <c r="S15" s="7" t="s">
         <v>37</v>
@@ -6921,7 +7049,9 @@
         <v>일반</v>
       </c>
       <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
+      <c r="Q16" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="R16" s="25"/>
       <c r="S16" s="7" t="s">
         <v>38</v>
@@ -6983,7 +7113,9 @@
         <v>일반</v>
       </c>
       <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
+      <c r="Q17" s="6" t="s">
+        <v>105</v>
+      </c>
       <c r="R17" s="25"/>
       <c r="S17" s="7" t="s">
         <v>39</v>
@@ -7045,7 +7177,9 @@
         <v>일반</v>
       </c>
       <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
+      <c r="Q18" s="6" t="s">
+        <v>106</v>
+      </c>
       <c r="R18" s="25"/>
       <c r="S18" s="7" t="s">
         <v>40</v>
@@ -7109,7 +7243,9 @@
       <c r="P19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q19" s="6"/>
+      <c r="Q19" s="6" t="s">
+        <v>107</v>
+      </c>
       <c r="R19" s="25"/>
       <c r="S19" s="7" t="s">
         <v>41</v>
@@ -7171,7 +7307,9 @@
         <v>일반</v>
       </c>
       <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
+      <c r="Q20" s="6" t="s">
+        <v>108</v>
+      </c>
       <c r="R20" s="25"/>
       <c r="S20" s="7" t="s">
         <v>42</v>
@@ -7233,7 +7371,9 @@
         <v>일반</v>
       </c>
       <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
+      <c r="Q21" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="R21" s="25"/>
       <c r="S21" s="7" t="s">
         <v>43</v>
@@ -7295,7 +7435,9 @@
         <v>일반</v>
       </c>
       <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
+      <c r="Q22" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="R22" s="25"/>
       <c r="S22" s="7" t="s">
         <v>44</v>
@@ -7359,7 +7501,9 @@
       <c r="P23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q23" s="6"/>
+      <c r="Q23" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="R23" s="25"/>
       <c r="S23" s="7" t="s">
         <v>45</v>
@@ -7421,7 +7565,9 @@
         <v>일반</v>
       </c>
       <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
+      <c r="Q24" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="R24" s="25"/>
       <c r="S24" s="7" t="s">
         <v>46</v>
@@ -7483,7 +7629,9 @@
         <v>일반</v>
       </c>
       <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
+      <c r="Q25" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="R25" s="25"/>
       <c r="S25" s="7" t="s">
         <v>47</v>
@@ -7547,7 +7695,9 @@
       <c r="P26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q26" s="6"/>
+      <c r="Q26" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="R26" s="25"/>
       <c r="S26" s="9" t="s">
         <v>48</v>
@@ -7611,7 +7761,9 @@
       <c r="P27" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Q27" s="6"/>
+      <c r="Q27" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="R27" s="25"/>
       <c r="S27" s="7" t="s">
         <v>49</v>
@@ -7673,7 +7825,9 @@
         <v>일반</v>
       </c>
       <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
+      <c r="Q28" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="R28" s="25"/>
       <c r="S28" s="9" t="s">
         <v>50</v>
@@ -7735,7 +7889,9 @@
         <v>일반</v>
       </c>
       <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
+      <c r="Q29" s="6" t="s">
+        <v>117</v>
+      </c>
       <c r="R29" s="25"/>
       <c r="S29" s="7" t="s">
         <v>51</v>
@@ -7797,7 +7953,9 @@
         <v>일반</v>
       </c>
       <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
+      <c r="Q30" s="6" t="s">
+        <v>118</v>
+      </c>
       <c r="R30" s="25"/>
       <c r="S30" s="7" t="s">
         <v>52</v>
@@ -7859,7 +8017,9 @@
         <v>일반</v>
       </c>
       <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
+      <c r="Q31" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="R31" s="25"/>
       <c r="S31" s="7" t="s">
         <v>53</v>
@@ -7921,7 +8081,9 @@
         <v>일반</v>
       </c>
       <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
+      <c r="Q32" s="6" t="s">
+        <v>120</v>
+      </c>
       <c r="R32" s="25"/>
       <c r="S32" s="9" t="s">
         <v>54</v>
@@ -8793,64 +8955,64 @@
       <c r="P3" s="18"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30" t="s">
+      <c r="D4" s="28"/>
+      <c r="E4" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30" t="s">
+      <c r="F4" s="28"/>
+      <c r="G4" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30" t="s">
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30" t="s">
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30" t="s">
+      <c r="D5" s="28"/>
+      <c r="E5" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31" t="s">
+      <c r="F5" s="28"/>
+      <c r="G5" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="30" t="s">
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30" t="s">
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="18"/>
@@ -8871,43 +9033,43 @@
       <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:19" ht="16.5" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29" t="s">
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="28" t="s">
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="28" t="s">
+      <c r="O7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="28" t="s">
+      <c r="P7" s="30" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="21" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="19" t="s">
         <v>69</v>
       </c>
@@ -8938,9 +9100,9 @@
       <c r="M8" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
       <c r="Q8" s="20"/>
       <c r="R8" s="20"/>
       <c r="S8" s="20"/>
@@ -10972,6 +11134,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:M7"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
@@ -10984,14 +11154,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:M7"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/25-새서울철도-강남구-보고서.xlsx
+++ b/25-새서울철도-강남구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2273,7 +2273,7 @@
         <v>신사역 #6번출구 앞도로(강남대로616)</v>
       </c>
       <c r="T32" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -2335,7 +2335,7 @@
         <v>삼주빌딩 앞도로(강남대로606)</v>
       </c>
       <c r="T33" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2397,7 +2397,7 @@
         <v>보림빌딩 청기와타운_신사점 앞도로(강남대로598)</v>
       </c>
       <c r="T34" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2459,7 +2459,7 @@
         <v>제이빌딩 NHN벅스 앞도로(강남대로586)</v>
       </c>
       <c r="T35" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -2521,7 +2521,7 @@
         <v>기아_강남영동지점 앞도로(강남대로580)</v>
       </c>
       <c r="T36" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2583,7 +2583,7 @@
         <v>전기공사공제조합회관 앞도로(강남대로574)</v>
       </c>
       <c r="T37" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2645,7 +2645,7 @@
         <v>선양빌딩 앞 도로(강남대로570)</v>
       </c>
       <c r="T38" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -2707,7 +2707,7 @@
         <v>신영와코루빌딩 앞 도로(강남대로566)</v>
       </c>
       <c r="T39" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2769,7 +2769,7 @@
         <v>강남빌딩 앞 도로(감남대로562)</v>
       </c>
       <c r="T40" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2831,7 +2831,7 @@
         <v>신성빌딩 파리바게트 앞도로(강남대로532)</v>
       </c>
       <c r="T41" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2893,7 +2893,7 @@
         <v>영동빌딩 광성약국 앞도로(강남대로520)</v>
       </c>
       <c r="T42" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2955,7 +2955,7 @@
         <v>광명빌딩 정관장 앞도로(강남대로506)</v>
       </c>
       <c r="T43" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -3017,7 +3017,7 @@
         <v>서희타워 아웃백 앞도로(강남대로502)</v>
       </c>
       <c r="T44" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -3079,7 +3079,7 @@
         <v>데이뷰의원_강남 앞도로(강남대로494)</v>
       </c>
       <c r="T45" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -3141,7 +3141,7 @@
         <v>99빌딩 앞 도로(강남대로484)</v>
       </c>
       <c r="T46" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -3203,7 +3203,7 @@
         <v>교차로 (봉은사로102)</v>
       </c>
       <c r="T47" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -3265,7 +3265,7 @@
         <v>한석타워 앞도로(강남대로456)</v>
       </c>
       <c r="T48" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -3327,12 +3327,384 @@
         <v>대연빌딩 앞 도로(강남대로452)</v>
       </c>
       <c r="T49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>26-19</v>
+      </c>
+      <c r="B50" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C50" t="str">
+        <v>26-강남구-19</v>
+      </c>
+      <c r="D50" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E50" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F50" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G50" t="str">
+        <v>3</v>
+      </c>
+      <c r="H50" t="str">
+        <v>-</v>
+      </c>
+      <c r="I50" t="str">
+        <v>0</v>
+      </c>
+      <c r="J50" t="str">
+        <v>3</v>
+      </c>
+      <c r="K50" t="str">
+        <v>0</v>
+      </c>
+      <c r="L50" t="str">
+        <v>0</v>
+      </c>
+      <c r="M50" t="str">
+        <v>0</v>
+      </c>
+      <c r="N50" t="str">
+        <v>3</v>
+      </c>
+      <c r="O50" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P50" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q50" t="str">
+        <v>역삼동814-5</v>
+      </c>
+      <c r="R50" t="str">
+        <v/>
+      </c>
+      <c r="S50" t="str">
+        <v>흥국생명빌딩 앞 도로(강남대로442)</v>
+      </c>
+      <c r="T50" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>26-20</v>
+      </c>
+      <c r="B51" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C51" t="str">
+        <v>26-강남구-20</v>
+      </c>
+      <c r="D51" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E51" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F51" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G51" t="str">
+        <v>3</v>
+      </c>
+      <c r="H51" t="str">
+        <v>-</v>
+      </c>
+      <c r="I51" t="str">
+        <v>0</v>
+      </c>
+      <c r="J51" t="str">
+        <v>3</v>
+      </c>
+      <c r="K51" t="str">
+        <v>0</v>
+      </c>
+      <c r="L51" t="str">
+        <v>0</v>
+      </c>
+      <c r="M51" t="str">
+        <v>0</v>
+      </c>
+      <c r="N51" t="str">
+        <v>3</v>
+      </c>
+      <c r="O51" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P51" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>역삼동814-6</v>
+      </c>
+      <c r="R51" t="str">
+        <v/>
+      </c>
+      <c r="S51" t="str">
+        <v>스타플렉스 앞 도로(강남대로438)</v>
+      </c>
+      <c r="T51" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>26-21</v>
+      </c>
+      <c r="B52" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C52" t="str">
+        <v>26-강남구-21</v>
+      </c>
+      <c r="D52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E52" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G52" t="str">
+        <v>3</v>
+      </c>
+      <c r="H52" t="str">
+        <v>-</v>
+      </c>
+      <c r="I52" t="str">
+        <v>0</v>
+      </c>
+      <c r="J52" t="str">
+        <v>3</v>
+      </c>
+      <c r="K52" t="str">
+        <v>0</v>
+      </c>
+      <c r="L52" t="str">
+        <v>0</v>
+      </c>
+      <c r="M52" t="str">
+        <v>0</v>
+      </c>
+      <c r="N52" t="str">
+        <v>3</v>
+      </c>
+      <c r="O52" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P52" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>역삼동815</v>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
+        <v>강남e스퀘어 앞 도로(강남대로432)</v>
+      </c>
+      <c r="T52" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>26-22</v>
+      </c>
+      <c r="B53" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C53" t="str">
+        <v>26-강남구-22</v>
+      </c>
+      <c r="D53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E53" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G53" t="str">
+        <v>3</v>
+      </c>
+      <c r="H53" t="str">
+        <v>-</v>
+      </c>
+      <c r="I53" t="str">
+        <v>0</v>
+      </c>
+      <c r="J53" t="str">
+        <v>3</v>
+      </c>
+      <c r="K53" t="str">
+        <v>0</v>
+      </c>
+      <c r="L53" t="str">
+        <v>0</v>
+      </c>
+      <c r="M53" t="str">
+        <v>0</v>
+      </c>
+      <c r="N53" t="str">
+        <v>3</v>
+      </c>
+      <c r="O53" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P53" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>역삼동815-4</v>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
+        <v>만이빌딩 앞 도로(강남대로428)</v>
+      </c>
+      <c r="T53" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>26-23</v>
+      </c>
+      <c r="B54" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C54" t="str">
+        <v>26-강남구-23</v>
+      </c>
+      <c r="D54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E54" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G54" t="str">
+        <v>3</v>
+      </c>
+      <c r="H54" t="str">
+        <v>-</v>
+      </c>
+      <c r="I54" t="str">
+        <v>0</v>
+      </c>
+      <c r="J54" t="str">
+        <v>3</v>
+      </c>
+      <c r="K54" t="str">
+        <v>0</v>
+      </c>
+      <c r="L54" t="str">
+        <v>0</v>
+      </c>
+      <c r="M54" t="str">
+        <v>0</v>
+      </c>
+      <c r="N54" t="str">
+        <v>3</v>
+      </c>
+      <c r="O54" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P54" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>역삼동815-5</v>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v>진우빌딩 일상비일상의틈 앞도로(426)</v>
+      </c>
+      <c r="T54" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>26-24</v>
+      </c>
+      <c r="B55" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C55" t="str">
+        <v>26-강남구-24</v>
+      </c>
+      <c r="D55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E55" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G55" t="str">
+        <v>3</v>
+      </c>
+      <c r="H55" t="str">
+        <v>-</v>
+      </c>
+      <c r="I55" t="str">
+        <v>0</v>
+      </c>
+      <c r="J55" t="str">
+        <v>3</v>
+      </c>
+      <c r="K55" t="str">
+        <v>0</v>
+      </c>
+      <c r="L55" t="str">
+        <v>0</v>
+      </c>
+      <c r="M55" t="str">
+        <v>0</v>
+      </c>
+      <c r="N55" t="str">
+        <v>3</v>
+      </c>
+      <c r="O55" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P55" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>역삼동816-2</v>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v>역삼빌딩 조앤조의원 앞 도로(강남대로420)</v>
+      </c>
+      <c r="T55" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T55"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-새서울철도-강남구-보고서.xlsx
+++ b/25-새서울철도-강남구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T55"/>
+  <dimension ref="A1:T54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,19 +485,19 @@
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-강남구-1</v>
+        <v>25-강남구-2</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
       </c>
       <c r="E5" t="str">
-        <v>종균열</v>
+        <v>-</v>
       </c>
       <c r="F5" t="str">
         <v>양호</v>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -524,428 +524,428 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="str">
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q5" t="str">
-        <v>신사동 501</v>
+        <v>논현동 17</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str" xml:space="preserve">
-        <v xml:space="preserve">우리은행 앞_x000d_
-도로_x000d_
-(강남대로)</v>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C6" t="str">
-        <v>25-강남구-2</v>
-      </c>
-      <c r="D6" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E6" t="str">
-        <v>-</v>
-      </c>
-      <c r="F6" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2</v>
-      </c>
-      <c r="H6" t="str">
-        <v>-</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P6" t="str">
-        <v>5cm미만 침하</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>논현동 17</v>
-      </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str" xml:space="preserve">
         <v xml:space="preserve">신사역 환기구 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C7" t="str">
+      <c r="T5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C6" t="str">
         <v>25-강남구-3</v>
       </c>
-      <c r="D7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E7" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F7" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="D6" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E6" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F6" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G6" t="str">
         <v>2</v>
       </c>
-      <c r="H7" t="str">
-        <v>-</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>3</v>
-      </c>
-      <c r="O7" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
+      <c r="H6" t="str">
+        <v>-</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
         <v>논현동 17-4</v>
       </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str" xml:space="preserve">
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str" xml:space="preserve">
         <v xml:space="preserve">청기와타운 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8">
+      <c r="T6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7">
         <v>4</v>
       </c>
-      <c r="B8" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C8" t="str">
+      <c r="B7" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C7" t="str">
         <v>25-강남구-4</v>
       </c>
-      <c r="D8" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E8" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F8" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G8" t="str">
+      <c r="D7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E7" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F7" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G7" t="str">
         <v>2</v>
       </c>
-      <c r="H8" t="str">
-        <v>-</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>3</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-      <c r="O8" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
+      <c r="H7" t="str">
+        <v>-</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
         <v>논현동 18-3</v>
       </c>
-      <c r="R8" t="str">
-        <v/>
-      </c>
-      <c r="S8" t="str" xml:space="preserve">
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str" xml:space="preserve">
         <v xml:space="preserve">NHN벅스 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9">
+      <c r="T7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
         <v>5</v>
       </c>
-      <c r="B9" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C9" t="str">
+      <c r="B8" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C8" t="str">
         <v>25-강남구-5</v>
       </c>
-      <c r="D9" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E9" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F9" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G9" t="str">
+      <c r="D8" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E8" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F8" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G8" t="str">
         <v>2</v>
       </c>
-      <c r="H9" t="str">
-        <v>-</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-      <c r="O9" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
+      <c r="H8" t="str">
+        <v>-</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
         <v>논현동 19-2</v>
       </c>
-      <c r="R9" t="str">
-        <v/>
-      </c>
-      <c r="S9" t="str" xml:space="preserve">
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str" xml:space="preserve">
         <v xml:space="preserve">성현빌딩 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10">
+      <c r="T8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
         <v>6</v>
       </c>
-      <c r="B10" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C10" t="str">
+      <c r="B9" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C9" t="str">
         <v>25-강남구-6</v>
       </c>
-      <c r="D10" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E10" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F10" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="D9" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E9" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F9" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G9" t="str">
         <v>2</v>
       </c>
-      <c r="H10" t="str">
-        <v>-</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>3</v>
-      </c>
-      <c r="O10" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
+      <c r="H9" t="str">
+        <v>-</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
         <v>논현동 49</v>
       </c>
-      <c r="R10" t="str">
-        <v/>
-      </c>
-      <c r="S10" t="str" xml:space="preserve">
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str" xml:space="preserve">
         <v xml:space="preserve">CU편의점 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11">
+      <c r="T9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
         <v>7</v>
       </c>
-      <c r="B11" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C11" t="str">
+      <c r="B10" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C10" t="str">
         <v>25-강남구-7</v>
       </c>
-      <c r="D11" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E11" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F11" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G11" t="str">
+      <c r="D10" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E10" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F10" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G10" t="str">
         <v>2</v>
       </c>
-      <c r="H11" t="str">
-        <v>-</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
+      <c r="H10" t="str">
+        <v>-</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="O10" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
         <v>논현동 49-17</v>
       </c>
-      <c r="R11" t="str">
-        <v/>
-      </c>
-      <c r="S11" t="str" xml:space="preserve">
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str" xml:space="preserve">
         <v xml:space="preserve">국제미디 논현점 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C11" t="str">
+        <v>25-강남구-8</v>
+      </c>
+      <c r="D11" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E11" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F11" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2</v>
+      </c>
+      <c r="H11" t="str">
+        <v>-</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v>논현동 50</v>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str" xml:space="preserve">
+        <v xml:space="preserve">논현역#9번출구 앞_x000d_
+도로_x000d_
+(강남대로)</v>
+      </c>
       <c r="T11" t="str">
         <v/>
       </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-강남구-8</v>
+        <v>25-강남구-9</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
       </c>
       <c r="E12" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F12" t="str">
         <v>양호</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -972,16 +972,16 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="str">
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q12" t="str">
-        <v>논현동 50</v>
+        <v>논현동 50-1</v>
       </c>
       <c r="R12" t="str">
         <v/>
@@ -997,19 +997,19 @@
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-강남구-9</v>
+        <v>25-강남구-10</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
       </c>
       <c r="E13" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F13" t="str">
         <v>양호</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1036,1193 +1036,1191 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="str">
         <v>일반</v>
       </c>
       <c r="P13" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
-        <v>논현동 50-1</v>
+        <v>논현동 120</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str" xml:space="preserve">
-        <v xml:space="preserve">논현역#9번출구 앞_x000d_
-도로_x000d_
-(강남대로)</v>
-      </c>
-      <c r="T13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C14" t="str">
-        <v>25-강남구-10</v>
-      </c>
-      <c r="D14" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E14" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F14" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G14" t="str">
-        <v>2</v>
-      </c>
-      <c r="H14" t="str">
-        <v>-</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>3</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>3</v>
-      </c>
-      <c r="O14" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
-        <v>논현동 120</v>
-      </c>
-      <c r="R14" t="str">
-        <v/>
-      </c>
-      <c r="S14" t="str" xml:space="preserve">
         <v xml:space="preserve">논현역 교차로_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15">
+      <c r="T13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14">
         <v>11</v>
       </c>
-      <c r="B15" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C15" t="str">
+      <c r="B14" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C14" t="str">
         <v>25-강남구-11</v>
       </c>
-      <c r="D15" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E15" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F15" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="D14" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E14" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F14" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G14" t="str">
         <v>2</v>
       </c>
-      <c r="H15" t="str">
-        <v>-</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>3</v>
-      </c>
-      <c r="O15" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
+      <c r="H14" t="str">
+        <v>-</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
         <v>논현동 164</v>
       </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str" xml:space="preserve">
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str" xml:space="preserve">
         <v xml:space="preserve">할리스커피 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16">
+      <c r="T14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15">
         <v>12</v>
       </c>
-      <c r="B16" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C16" t="str">
+      <c r="B15" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C15" t="str">
         <v>25-강남구-12</v>
       </c>
-      <c r="D16" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E16" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F16" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G16" t="str">
+      <c r="D15" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E15" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F15" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G15" t="str">
         <v>2</v>
       </c>
-      <c r="H16" t="str">
-        <v>-</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>3</v>
-      </c>
-      <c r="O16" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
+      <c r="H15" t="str">
+        <v>-</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
         <v>논현동 164-4</v>
       </c>
-      <c r="R16" t="str">
-        <v/>
-      </c>
-      <c r="S16" t="str" xml:space="preserve">
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str" xml:space="preserve">
         <v xml:space="preserve">한국금거래소_x000d_
 강남논현점 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17">
+      <c r="T15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16">
         <v>13</v>
       </c>
-      <c r="B17" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C17" t="str">
+      <c r="B16" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C16" t="str">
         <v>25-강남구-13</v>
       </c>
-      <c r="D17" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E17" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F17" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G17" t="str">
+      <c r="D16" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E16" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F16" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G16" t="str">
         <v>2</v>
       </c>
-      <c r="H17" t="str">
-        <v>-</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>3</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>3</v>
-      </c>
-      <c r="O17" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
+      <c r="H16" t="str">
+        <v>-</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
         <v>논현동 165</v>
       </c>
-      <c r="R17" t="str">
-        <v/>
-      </c>
-      <c r="S17" t="str" xml:space="preserve">
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str" xml:space="preserve">
         <v xml:space="preserve">아웃백 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18">
+      <c r="T16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17">
         <v>14</v>
       </c>
-      <c r="B18" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C18" t="str">
+      <c r="B17" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C17" t="str">
         <v>25-강남구-14</v>
       </c>
-      <c r="D18" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E18" t="str">
-        <v>-</v>
-      </c>
-      <c r="F18" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G18" t="str">
+      <c r="D17" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E17" t="str">
+        <v>-</v>
+      </c>
+      <c r="F17" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G17" t="str">
         <v>2</v>
       </c>
-      <c r="H18" t="str">
-        <v>-</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P18" t="str">
+      <c r="H17" t="str">
+        <v>-</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P17" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="Q17" t="str">
         <v>논현동 165-8</v>
       </c>
-      <c r="R18" t="str">
-        <v/>
-      </c>
-      <c r="S18" t="str" xml:space="preserve">
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str" xml:space="preserve">
         <v xml:space="preserve">나나성형_x000d_
 외과의원 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19">
+      <c r="T17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18">
         <v>15</v>
       </c>
-      <c r="B19" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C19" t="str">
+      <c r="B18" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C18" t="str">
         <v>25-강남구-15</v>
       </c>
-      <c r="D19" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E19" t="str">
+      <c r="D18" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E18" t="str">
         <v>종균열</v>
       </c>
-      <c r="F19" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G19" t="str">
+      <c r="F18" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G18" t="str">
         <v>2</v>
       </c>
-      <c r="H19" t="str">
-        <v>-</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
+      <c r="H18" t="str">
+        <v>-</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
         <v>1</v>
       </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
         <v>1</v>
       </c>
-      <c r="O19" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
+      <c r="O18" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
         <v>논현동 199</v>
       </c>
-      <c r="R19" t="str">
-        <v/>
-      </c>
-      <c r="S19" t="str" xml:space="preserve">
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str" xml:space="preserve">
         <v xml:space="preserve">나나성형_x000d_
 외과의원 앞_x000d_
 횡단도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20">
+      <c r="T18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19">
         <v>16</v>
       </c>
-      <c r="B20" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C20" t="str">
+      <c r="B19" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C19" t="str">
         <v>25-강남구-16</v>
       </c>
-      <c r="D20" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E20" t="str">
+      <c r="D19" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E19" t="str">
         <v>종균열</v>
       </c>
-      <c r="F20" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G20" t="str">
+      <c r="F19" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G19" t="str">
         <v>2</v>
       </c>
-      <c r="H20" t="str">
-        <v>-</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
+      <c r="H19" t="str">
+        <v>-</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
         <v>1</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>1</v>
       </c>
-      <c r="O20" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
-      <c r="Q20" t="str">
+      <c r="O19" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
         <v>논현동 200-7</v>
       </c>
-      <c r="R20" t="str">
-        <v/>
-      </c>
-      <c r="S20" t="str" xml:space="preserve">
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str" xml:space="preserve">
         <v xml:space="preserve">신논현역#3번출 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21">
+      <c r="T19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20">
         <v>17</v>
       </c>
-      <c r="B21" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C21" t="str">
+      <c r="B20" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C20" t="str">
         <v>25-강남구-17</v>
       </c>
-      <c r="D21" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E21" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F21" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G21" t="str">
+      <c r="D20" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E20" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F20" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G20" t="str">
         <v>2</v>
       </c>
-      <c r="H21" t="str">
-        <v>-</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>3</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>3</v>
-      </c>
-      <c r="O21" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
+      <c r="H20" t="str">
+        <v>-</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
         <v>역삼동 808</v>
       </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
-      <c r="S21" t="str" xml:space="preserve">
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str" xml:space="preserve">
         <v xml:space="preserve">아디다스 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22">
+      <c r="T20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21">
         <v>18</v>
       </c>
-      <c r="B22" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C22" t="str">
+      <c r="B21" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C21" t="str">
         <v>25-강남구-18</v>
       </c>
-      <c r="D22" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E22" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F22" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="D21" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E21" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F21" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G21" t="str">
         <v>2</v>
       </c>
-      <c r="H22" t="str">
-        <v>-</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>3</v>
-      </c>
-      <c r="O22" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P22" t="str">
+      <c r="H21" t="str">
+        <v>-</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P21" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="Q21" t="str">
         <v>역삼동 808-4</v>
       </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str" xml:space="preserve">
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str" xml:space="preserve">
         <v xml:space="preserve">신논현역 #5번출구 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23">
+      <c r="T21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22">
         <v>19</v>
       </c>
-      <c r="B23" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C23" t="str">
+      <c r="B22" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C22" t="str">
         <v>25-강남구-19</v>
       </c>
-      <c r="D23" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E23" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F23" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G23" t="str">
+      <c r="D22" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E22" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F22" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G22" t="str">
         <v>2</v>
       </c>
-      <c r="H23" t="str">
-        <v>-</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>3</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>3</v>
-      </c>
-      <c r="O23" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-      <c r="Q23" t="str">
+      <c r="H22" t="str">
+        <v>-</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
         <v>역삼동 809-12</v>
       </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str" xml:space="preserve">
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str" xml:space="preserve">
         <v xml:space="preserve">뮤즈의원 강남점 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
-      <c r="A24">
+      <c r="T22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23">
         <v>20</v>
       </c>
-      <c r="B24" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C24" t="str">
+      <c r="B23" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C23" t="str">
         <v>25-강남구-20</v>
       </c>
-      <c r="D24" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E24" t="str">
+      <c r="D23" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E23" t="str">
         <v>종균열</v>
       </c>
-      <c r="F24" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G24" t="str">
+      <c r="F23" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G23" t="str">
         <v>2</v>
       </c>
-      <c r="H24" t="str">
-        <v>-</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
+      <c r="H23" t="str">
+        <v>-</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
         <v>1</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
         <v>1</v>
       </c>
-      <c r="O24" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
+      <c r="O23" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
         <v>역삼동 814-5</v>
       </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str" xml:space="preserve">
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str" xml:space="preserve">
         <v xml:space="preserve">커피빈 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25">
+      <c r="T23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24">
         <v>21</v>
       </c>
-      <c r="B25" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C25" t="str">
+      <c r="B24" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C24" t="str">
         <v>25-강남구-21</v>
       </c>
-      <c r="D25" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E25" t="str">
-        <v>-</v>
-      </c>
-      <c r="F25" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G25" t="str">
+      <c r="D24" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E24" t="str">
+        <v>-</v>
+      </c>
+      <c r="F24" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G24" t="str">
         <v>2</v>
       </c>
-      <c r="H25" t="str">
-        <v>-</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P25" t="str">
+      <c r="H24" t="str">
+        <v>-</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P24" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q25" t="str">
+      <c r="Q24" t="str">
         <v>역삼동 814-6</v>
       </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str" xml:space="preserve">
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str" xml:space="preserve">
         <v xml:space="preserve">CGV 앞_x000d_
 횡단보도_x000d_
 (강남대로)</v>
       </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26">
+      <c r="T24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25">
         <v>22</v>
       </c>
-      <c r="B26" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C26" t="str">
+      <c r="B25" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C25" t="str">
         <v>25-강남구-22</v>
       </c>
-      <c r="D26" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E26" t="str">
-        <v>-</v>
-      </c>
-      <c r="F26" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G26" t="str">
+      <c r="D25" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E25" t="str">
+        <v>-</v>
+      </c>
+      <c r="F25" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G25" t="str">
         <v>2</v>
       </c>
-      <c r="H26" t="str">
-        <v>-</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P26" t="str">
+      <c r="H25" t="str">
+        <v>-</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P25" t="str">
         <v>5cm미만 침하</v>
       </c>
-      <c r="Q26" t="str">
+      <c r="Q25" t="str">
         <v>역삼동 815</v>
       </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str" xml:space="preserve">
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str" xml:space="preserve">
         <v xml:space="preserve">강남e스퀘어 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27">
+      <c r="T25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26">
         <v>23</v>
       </c>
-      <c r="B27" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C27" t="str">
+      <c r="B26" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C26" t="str">
         <v>25-강남구-23</v>
       </c>
-      <c r="D27" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E27" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F27" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G27" t="str">
+      <c r="D26" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E26" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F26" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G26" t="str">
         <v>2</v>
       </c>
-      <c r="H27" t="str">
-        <v>-</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>3</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>3</v>
-      </c>
-      <c r="O27" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
-      <c r="Q27" t="str">
+      <c r="H26" t="str">
+        <v>-</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
         <v>역삼동 815-2</v>
       </c>
-      <c r="R27" t="str">
-        <v/>
-      </c>
-      <c r="S27" t="str" xml:space="preserve">
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str" xml:space="preserve">
         <v xml:space="preserve">ABC마트 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28">
+      <c r="T26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27">
         <v>24</v>
       </c>
-      <c r="B28" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C28" t="str">
+      <c r="B27" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C27" t="str">
         <v>25-강남구-24</v>
       </c>
-      <c r="D28" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E28" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F28" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G28" t="str">
+      <c r="D27" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E27" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F27" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G27" t="str">
         <v>2</v>
       </c>
-      <c r="H28" t="str">
-        <v>-</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>3</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>3</v>
-      </c>
-      <c r="O28" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P28" t="str">
-        <v/>
-      </c>
-      <c r="Q28" t="str">
+      <c r="H27" t="str">
+        <v>-</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
         <v>역삼동 815-5</v>
       </c>
-      <c r="R28" t="str">
-        <v/>
-      </c>
-      <c r="S28" t="str" xml:space="preserve">
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str" xml:space="preserve">
         <v xml:space="preserve">진우빌딩 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29">
+      <c r="T27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28">
         <v>25</v>
       </c>
-      <c r="B29" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C29" t="str">
+      <c r="B28" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C28" t="str">
         <v>25-강남구-25</v>
       </c>
-      <c r="D29" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E29" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F29" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G29" t="str">
+      <c r="D28" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E28" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F28" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G28" t="str">
         <v>2</v>
       </c>
-      <c r="H29" t="str">
-        <v>-</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>3</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-      <c r="O29" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P29" t="str">
-        <v/>
-      </c>
-      <c r="Q29" t="str">
+      <c r="H28" t="str">
+        <v>-</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
         <v>역삼동 820</v>
       </c>
-      <c r="R29" t="str">
-        <v/>
-      </c>
-      <c r="S29" t="str" xml:space="preserve">
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str" xml:space="preserve">
         <v xml:space="preserve">뉴발란스 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30">
+      <c r="T28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29">
         <v>26</v>
       </c>
-      <c r="B30" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C30" t="str">
+      <c r="B29" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C29" t="str">
         <v>25-강남구-26</v>
       </c>
-      <c r="D30" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E30" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F30" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G30" t="str">
+      <c r="D29" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E29" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F29" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G29" t="str">
         <v>2</v>
       </c>
-      <c r="H30" t="str">
-        <v>-</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>3</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>3</v>
-      </c>
-      <c r="O30" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P30" t="str">
-        <v/>
-      </c>
-      <c r="Q30" t="str">
+      <c r="H29" t="str">
+        <v>-</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
         <v>역삼동 820-8</v>
       </c>
-      <c r="R30" t="str">
-        <v/>
-      </c>
-      <c r="S30" t="str" xml:space="preserve">
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str" xml:space="preserve">
         <v xml:space="preserve">디자인스킨 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
-      <c r="T30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31">
+      <c r="T29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30">
         <v>27</v>
       </c>
-      <c r="B31" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C31" t="str">
+      <c r="B30" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C30" t="str">
         <v>25-강남구-27</v>
       </c>
-      <c r="D31" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E31" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F31" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G31" t="str">
+      <c r="D30" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E30" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F30" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G30" t="str">
         <v>2</v>
       </c>
-      <c r="H31" t="str">
-        <v>-</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>3</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>3</v>
-      </c>
-      <c r="O31" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P31" t="str">
-        <v/>
-      </c>
-      <c r="Q31" t="str">
+      <c r="H30" t="str">
+        <v>-</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
         <v>역삼동 820-9</v>
       </c>
-      <c r="R31" t="str">
-        <v/>
-      </c>
-      <c r="S31" t="str" xml:space="preserve">
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str" xml:space="preserve">
         <v xml:space="preserve">SC제일은행 앞_x000d_
 도로_x000d_
 (강남대로)</v>
       </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>26-01</v>
+      </c>
+      <c r="B31" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C31" t="str">
+        <v>26-강남구-01</v>
+      </c>
+      <c r="D31" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E31" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F31" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G31" t="str">
+        <v>3</v>
+      </c>
+      <c r="H31" t="str">
+        <v>-</v>
+      </c>
+      <c r="I31" t="str">
+        <v>0</v>
+      </c>
+      <c r="J31" t="str">
+        <v>3</v>
+      </c>
+      <c r="K31" t="str">
+        <v>0</v>
+      </c>
+      <c r="L31" t="str">
+        <v>0</v>
+      </c>
+      <c r="M31" t="str">
+        <v>0</v>
+      </c>
+      <c r="N31" t="str">
+        <v>3</v>
+      </c>
+      <c r="O31" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P31" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>신사동501</v>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v>신사역 #6번출구 앞도로(강남대로616)</v>
+      </c>
       <c r="T31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>26-강남구-01</v>
+        <v>26-강남구-02</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
@@ -2264,13 +2262,13 @@
         <v>-</v>
       </c>
       <c r="Q32" t="str">
-        <v>신사동501</v>
+        <v>논현동1</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>신사역 #6번출구 앞도로(강남대로616)</v>
+        <v>삼주빌딩 앞도로(강남대로606)</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2278,13 +2276,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>26-강남구-02</v>
+        <v>26-강남구-03</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
@@ -2326,13 +2324,13 @@
         <v>-</v>
       </c>
       <c r="Q33" t="str">
-        <v>논현동1</v>
+        <v>논현동17-4</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>삼주빌딩 앞도로(강남대로606)</v>
+        <v>보림빌딩 청기와타운_신사점 앞도로(강남대로598)</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2340,13 +2338,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>26-강남구-03</v>
+        <v>26-강남구-04</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
@@ -2388,13 +2386,13 @@
         <v>-</v>
       </c>
       <c r="Q34" t="str">
-        <v>논현동17-4</v>
+        <v>논현동18-3</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>보림빌딩 청기와타운_신사점 앞도로(강남대로598)</v>
+        <v>제이빌딩 NHN벅스 앞도로(강남대로586)</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2402,13 +2400,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B35" t="str">
         <v>강남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>26-강남구-04</v>
+        <v>26-강남구-05</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
@@ -2450,13 +2448,13 @@
         <v>-</v>
       </c>
       <c r="Q35" t="str">
-        <v>논현동18-3</v>
+        <v>논현동19</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>제이빌딩 NHN벅스 앞도로(강남대로586)</v>
+        <v>기아_강남영동지점 앞도로(강남대로580)</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2464,13 +2462,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B36" t="str">
         <v>강남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>26-강남구-05</v>
+        <v>26-강남구-06</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2512,13 +2510,13 @@
         <v>-</v>
       </c>
       <c r="Q36" t="str">
-        <v>논현동19</v>
+        <v>논현동19-7</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>기아_강남영동지점 앞도로(강남대로580)</v>
+        <v>전기공사공제조합회관 앞도로(강남대로574)</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2526,13 +2524,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B37" t="str">
         <v>강남대로</v>
       </c>
       <c r="C37" t="str">
-        <v>26-강남구-06</v>
+        <v>26-강남구-07</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2574,13 +2572,13 @@
         <v>-</v>
       </c>
       <c r="Q37" t="str">
-        <v>논현동19-7</v>
+        <v>논현동49</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>전기공사공제조합회관 앞도로(강남대로574)</v>
+        <v>선양빌딩 앞 도로(강남대로570)</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2588,13 +2586,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B38" t="str">
         <v>강남대로</v>
       </c>
       <c r="C38" t="str">
-        <v>26-강남구-07</v>
+        <v>26-강남구-08</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2636,13 +2634,13 @@
         <v>-</v>
       </c>
       <c r="Q38" t="str">
-        <v>논현동49</v>
+        <v>논현동49-4</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>선양빌딩 앞 도로(강남대로570)</v>
+        <v>신영와코루빌딩 앞 도로(강남대로566)</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2650,13 +2648,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B39" t="str">
         <v>강남대로</v>
       </c>
       <c r="C39" t="str">
-        <v>26-강남구-08</v>
+        <v>26-강남구-09</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2698,13 +2696,13 @@
         <v>-</v>
       </c>
       <c r="Q39" t="str">
-        <v>논현동49-4</v>
+        <v>논현동49-17</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>신영와코루빌딩 앞 도로(강남대로566)</v>
+        <v>강남빌딩 앞 도로(감남대로562)</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2712,19 +2710,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B40" t="str">
         <v>강남대로</v>
       </c>
       <c r="C40" t="str">
-        <v>26-강남구-09</v>
+        <v>26-강남구-10</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
       </c>
       <c r="E40" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F40" t="str">
         <v>양호</v>
@@ -2739,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K40" t="str">
         <v>0</v>
@@ -2751,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O40" t="str">
         <v>일반</v>
@@ -2760,13 +2758,13 @@
         <v>-</v>
       </c>
       <c r="Q40" t="str">
-        <v>논현동49-17</v>
+        <v>논현동143</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>강남빌딩 앞 도로(감남대로562)</v>
+        <v>신성빌딩 파리바게트 앞도로(강남대로532)</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2774,19 +2772,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B41" t="str">
         <v>강남대로</v>
       </c>
       <c r="C41" t="str">
-        <v>26-강남구-10</v>
+        <v>26-강남구-11</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
       </c>
       <c r="E41" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F41" t="str">
         <v>양호</v>
@@ -2801,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41" t="str">
         <v>0</v>
@@ -2813,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O41" t="str">
         <v>일반</v>
@@ -2822,13 +2820,13 @@
         <v>-</v>
       </c>
       <c r="Q41" t="str">
-        <v>논현동143</v>
+        <v>논현동164</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>신성빌딩 파리바게트 앞도로(강남대로532)</v>
+        <v>영동빌딩 광성약국 앞도로(강남대로520)</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2836,13 +2834,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B42" t="str">
         <v>강남대로</v>
       </c>
       <c r="C42" t="str">
-        <v>26-강남구-11</v>
+        <v>26-강남구-12</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
@@ -2884,13 +2882,13 @@
         <v>-</v>
       </c>
       <c r="Q42" t="str">
-        <v>논현동164</v>
+        <v>논현동164-11</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>영동빌딩 광성약국 앞도로(강남대로520)</v>
+        <v>광명빌딩 정관장 앞도로(강남대로506)</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2898,13 +2896,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B43" t="str">
         <v>강남대로</v>
       </c>
       <c r="C43" t="str">
-        <v>26-강남구-12</v>
+        <v>26-강남구-13</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
@@ -2943,16 +2941,16 @@
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v>-</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q43" t="str">
-        <v>논현동164-11</v>
+        <v>논현동165</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>광명빌딩 정관장 앞도로(강남대로506)</v>
+        <v>서희타워 아웃백 앞도로(강남대로502)</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2960,13 +2958,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B44" t="str">
         <v>강남대로</v>
       </c>
       <c r="C44" t="str">
-        <v>26-강남구-13</v>
+        <v>26-강남구-14</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
@@ -3005,16 +3003,16 @@
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v>5cm미만 침하</v>
+        <v>-</v>
       </c>
       <c r="Q44" t="str">
-        <v>논현동165</v>
+        <v>논현동165-7</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>서희타워 아웃백 앞도로(강남대로502)</v>
+        <v>데이뷰의원_강남 앞도로(강남대로494)</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -3022,13 +3020,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B45" t="str">
         <v>강남대로</v>
       </c>
       <c r="C45" t="str">
-        <v>26-강남구-14</v>
+        <v>26-강남구-15</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
@@ -3070,13 +3068,13 @@
         <v>-</v>
       </c>
       <c r="Q45" t="str">
-        <v>논현동165-7</v>
+        <v>논현동199-2</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>데이뷰의원_강남 앞도로(강남대로494)</v>
+        <v>99빌딩 앞 도로(강남대로484)</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3084,13 +3082,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B46" t="str">
         <v>강남대로</v>
       </c>
       <c r="C46" t="str">
-        <v>26-강남구-15</v>
+        <v>26-강남구-16</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
@@ -3132,13 +3130,13 @@
         <v>-</v>
       </c>
       <c r="Q46" t="str">
-        <v>논현동199-2</v>
+        <v>교보타워사거리</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>99빌딩 앞 도로(강남대로484)</v>
+        <v>교차로 (봉은사로102)</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3146,25 +3144,25 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B47" t="str">
         <v>강남대로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-강남구-16</v>
+        <v>26-강남구-17</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
       </c>
       <c r="G47" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47" t="str">
         <v>-</v>
@@ -3173,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K47" t="str">
         <v>0</v>
@@ -3185,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O47" t="str">
         <v>일반</v>
@@ -3194,13 +3192,13 @@
         <v>-</v>
       </c>
       <c r="Q47" t="str">
-        <v>교보타워사거리</v>
+        <v>역삼동809-10</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>교차로 (봉은사로102)</v>
+        <v>한석타워 앞도로(강남대로456)</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3208,25 +3206,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B48" t="str">
         <v>강남대로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-강남구-17</v>
+        <v>26-강남구-18</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
       </c>
       <c r="G48" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" t="str">
         <v>-</v>
@@ -3235,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K48" t="str">
         <v>0</v>
@@ -3247,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O48" t="str">
         <v>일반</v>
@@ -3256,13 +3254,13 @@
         <v>-</v>
       </c>
       <c r="Q48" t="str">
-        <v>역삼동809-10</v>
+        <v>역삼동809-12</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>한석타워 앞도로(강남대로456)</v>
+        <v>대연빌딩 앞 도로(강남대로452)</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3270,13 +3268,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B49" t="str">
         <v>강남대로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-강남구-18</v>
+        <v>26-강남구-19</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3318,13 +3316,13 @@
         <v>-</v>
       </c>
       <c r="Q49" t="str">
-        <v>역삼동809-12</v>
+        <v>역삼동814-5</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>대연빌딩 앞 도로(강남대로452)</v>
+        <v>흥국생명빌딩 앞 도로(강남대로442)</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3332,13 +3330,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B50" t="str">
         <v>강남대로</v>
       </c>
       <c r="C50" t="str">
-        <v>26-강남구-19</v>
+        <v>26-강남구-20</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3380,27 +3378,27 @@
         <v>-</v>
       </c>
       <c r="Q50" t="str">
-        <v>역삼동814-5</v>
+        <v>역삼동814-6</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>흥국생명빌딩 앞 도로(강남대로442)</v>
+        <v>스타플렉스 앞 도로(강남대로438)</v>
       </c>
       <c r="T50" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B51" t="str">
         <v>강남대로</v>
       </c>
       <c r="C51" t="str">
-        <v>26-강남구-20</v>
+        <v>26-강남구-21</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3442,27 +3440,27 @@
         <v>-</v>
       </c>
       <c r="Q51" t="str">
-        <v>역삼동814-6</v>
+        <v>역삼동815</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>스타플렉스 앞 도로(강남대로438)</v>
+        <v>강남e스퀘어 앞 도로(강남대로432)</v>
       </c>
       <c r="T51" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B52" t="str">
         <v>강남대로</v>
       </c>
       <c r="C52" t="str">
-        <v>26-강남구-21</v>
+        <v>26-강남구-22</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3504,27 +3502,27 @@
         <v>-</v>
       </c>
       <c r="Q52" t="str">
-        <v>역삼동815</v>
+        <v>역삼동815-4</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>강남e스퀘어 앞 도로(강남대로432)</v>
+        <v>만이빌딩 앞 도로(강남대로428)</v>
       </c>
       <c r="T52" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B53" t="str">
         <v>강남대로</v>
       </c>
       <c r="C53" t="str">
-        <v>26-강남구-22</v>
+        <v>26-강남구-23</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3566,27 +3564,27 @@
         <v>-</v>
       </c>
       <c r="Q53" t="str">
-        <v>역삼동815-4</v>
+        <v>역삼동815-5</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>만이빌딩 앞 도로(강남대로428)</v>
+        <v>진우빌딩 일상비일상의틈 앞도로(426)</v>
       </c>
       <c r="T53" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B54" t="str">
         <v>강남대로</v>
       </c>
       <c r="C54" t="str">
-        <v>26-강남구-23</v>
+        <v>26-강남구-24</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3628,83 +3626,21 @@
         <v>-</v>
       </c>
       <c r="Q54" t="str">
-        <v>역삼동815-5</v>
+        <v>역삼동816-2</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>진우빌딩 일상비일상의틈 앞도로(426)</v>
+        <v>역삼빌딩 조앤조의원 앞 도로(강남대로420)</v>
       </c>
       <c r="T54" t="str">
-        <v>현장확인필요</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>26-24</v>
-      </c>
-      <c r="B55" t="str">
-        <v>강남대로</v>
-      </c>
-      <c r="C55" t="str">
-        <v>26-강남구-24</v>
-      </c>
-      <c r="D55" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E55" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F55" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G55" t="str">
-        <v>3</v>
-      </c>
-      <c r="H55" t="str">
-        <v>-</v>
-      </c>
-      <c r="I55" t="str">
-        <v>0</v>
-      </c>
-      <c r="J55" t="str">
-        <v>3</v>
-      </c>
-      <c r="K55" t="str">
-        <v>0</v>
-      </c>
-      <c r="L55" t="str">
-        <v>0</v>
-      </c>
-      <c r="M55" t="str">
-        <v>0</v>
-      </c>
-      <c r="N55" t="str">
-        <v>3</v>
-      </c>
-      <c r="O55" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P55" t="str">
-        <v>-</v>
-      </c>
-      <c r="Q55" t="str">
-        <v>역삼동816-2</v>
-      </c>
-      <c r="R55" t="str">
-        <v/>
-      </c>
-      <c r="S55" t="str">
-        <v>역삼빌딩 조앤조의원 앞 도로(강남대로420)</v>
-      </c>
-      <c r="T55" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T54"/>
   </ignoredErrors>
 </worksheet>
 </file>